--- a/data/Sample Log/Sierra_Nevada_Lakes_AA_Sample_Log.xlsx
+++ b/data/Sample Log/Sierra_Nevada_Lakes_AA_Sample_Log.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10116"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/AlexiBesser/Dropbox/Sierra Nevada Lakes AA Isotopes/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chriswall/Desktop/Research and Teaching/github/Sierra-plankton-CSIA/data/Sample Log/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D91C32A3-1A6A-3E4E-8DD0-70CE715F93D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E98E8F82-A4B9-764A-8F8C-7379C78EC369}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="32600" windowHeight="20500" activeTab="1" xr2:uid="{A61E4CAC-973D-E849-8F20-A33A2B434430}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" activeTab="2" xr2:uid="{A61E4CAC-973D-E849-8F20-A33A2B434430}"/>
   </bookViews>
   <sheets>
     <sheet name="All Samples" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1302" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1392" uniqueCount="348">
   <si>
     <t>Sample ID</t>
   </si>
@@ -1498,6 +1498,12 @@
   <si>
     <t>08Feb2023.r1731/08Feb2023.r1732</t>
   </si>
+  <si>
+    <t>notes</t>
+  </si>
+  <si>
+    <t>average.chl.ug/L</t>
+  </si>
 </sst>
 </file>
 
@@ -1667,7 +1673,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -1727,11 +1733,29 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1903,6 +1927,10 @@
     <xf numFmtId="15" fontId="13" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1921,9 +1949,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1961,7 +1989,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2067,7 +2095,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2209,7 +2237,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -6147,7 +6175,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8809DD68-14B7-4392-9F23-E8657B3C7E0C}">
-  <dimension ref="A1:AK987"/>
+  <dimension ref="A1:AK986"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16.83203125" style="16" customWidth="1"/>
@@ -6157,7 +6185,7 @@
     <col min="5" max="5" width="13" style="16" customWidth="1"/>
     <col min="6" max="6" width="12.1640625" style="16" customWidth="1"/>
     <col min="7" max="7" width="9" style="16"/>
-    <col min="8" max="8" width="9"/>
+    <col min="8" max="8" width="14.33203125" customWidth="1"/>
     <col min="18" max="18" width="16.5" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6203,82 +6231,82 @@
       <c r="AK1" s="58"/>
     </row>
     <row r="2" spans="1:37" x14ac:dyDescent="0.2">
-      <c r="A2" s="58" t="s">
+      <c r="A2" s="71" t="s">
         <v>117</v>
       </c>
-      <c r="B2" s="58" t="s">
+      <c r="B2" s="71" t="s">
         <v>118</v>
       </c>
-      <c r="C2" s="58" t="s">
+      <c r="C2" s="71" t="s">
         <v>119</v>
       </c>
-      <c r="D2" s="58" t="s">
+      <c r="D2" s="71" t="s">
         <v>259</v>
       </c>
-      <c r="E2" s="58" t="s">
+      <c r="E2" s="71" t="s">
         <v>120</v>
       </c>
-      <c r="F2" s="58" t="s">
+      <c r="F2" s="71" t="s">
         <v>121</v>
       </c>
-      <c r="G2" s="58" t="s">
+      <c r="G2" s="71" t="s">
         <v>260</v>
       </c>
-      <c r="H2" s="58" t="s">
+      <c r="H2" s="71" t="s">
         <v>122</v>
       </c>
-      <c r="I2" s="58" t="s">
+      <c r="I2" s="71" t="s">
         <v>261</v>
       </c>
-      <c r="J2" s="58" t="s">
+      <c r="J2" s="71" t="s">
         <v>262</v>
       </c>
-      <c r="K2" s="58" t="s">
+      <c r="K2" s="71" t="s">
         <v>263</v>
       </c>
-      <c r="L2" s="58" t="s">
+      <c r="L2" s="71" t="s">
         <v>123</v>
       </c>
-      <c r="M2" s="58" t="s">
+      <c r="M2" s="71" t="s">
         <v>124</v>
       </c>
-      <c r="N2" s="58" t="s">
+      <c r="N2" s="71" t="s">
         <v>125</v>
       </c>
-      <c r="O2" s="58" t="s">
+      <c r="O2" s="71" t="s">
         <v>126</v>
       </c>
-      <c r="P2" s="58" t="s">
+      <c r="P2" s="71" t="s">
         <v>127</v>
       </c>
-      <c r="Q2" s="58" t="s">
+      <c r="Q2" s="71" t="s">
         <v>128</v>
       </c>
-      <c r="R2" s="58" t="s">
+      <c r="R2" s="71" t="s">
         <v>264</v>
       </c>
-      <c r="S2" s="58" t="s">
+      <c r="S2" s="71" t="s">
         <v>265</v>
       </c>
-      <c r="T2" s="58" t="s">
+      <c r="T2" s="71" t="s">
         <v>266</v>
       </c>
-      <c r="U2" s="58" t="s">
+      <c r="U2" s="71" t="s">
         <v>267</v>
       </c>
-      <c r="V2" s="58" t="s">
+      <c r="V2" s="71" t="s">
         <v>268</v>
       </c>
-      <c r="W2" s="58" t="s">
+      <c r="W2" s="71" t="s">
         <v>269</v>
       </c>
-      <c r="X2" s="58" t="s">
+      <c r="X2" s="71" t="s">
         <v>270</v>
       </c>
-      <c r="Y2" s="58" t="s">
+      <c r="Y2" s="71" t="s">
         <v>271</v>
       </c>
-      <c r="Z2" s="58"/>
+      <c r="Z2" s="71"/>
       <c r="AA2" s="58"/>
       <c r="AB2" s="58"/>
       <c r="AC2" s="58"/>
@@ -7150,80 +7178,80 @@
       <c r="AK12" s="58"/>
     </row>
     <row r="13" spans="1:37" x14ac:dyDescent="0.2">
-      <c r="A13" s="58" t="s">
+      <c r="A13" s="71" t="s">
         <v>129</v>
       </c>
-      <c r="B13" s="59">
+      <c r="B13" s="72">
         <v>44784</v>
       </c>
-      <c r="C13" s="58" t="s">
+      <c r="C13" s="71" t="s">
         <v>133</v>
       </c>
-      <c r="D13" s="58" t="s">
+      <c r="D13" s="71" t="s">
         <v>258</v>
       </c>
-      <c r="E13" s="58">
+      <c r="E13" s="71">
         <v>37.98977</v>
       </c>
-      <c r="F13" s="58">
+      <c r="F13" s="71">
         <v>-119.30625999999999</v>
       </c>
-      <c r="G13" s="58">
+      <c r="G13" s="71">
         <v>3140</v>
       </c>
-      <c r="H13" s="58">
+      <c r="H13" s="71">
         <v>34.6</v>
       </c>
-      <c r="I13" s="58" t="s">
+      <c r="I13" s="71" t="s">
         <v>17</v>
       </c>
-      <c r="J13" s="58" t="s">
+      <c r="J13" s="71" t="s">
         <v>17</v>
       </c>
-      <c r="K13" s="58" t="s">
+      <c r="K13" s="71" t="s">
         <v>17</v>
       </c>
-      <c r="L13" s="58">
+      <c r="L13" s="71">
         <v>13.85</v>
       </c>
-      <c r="M13" s="58">
+      <c r="M13" s="71">
         <v>71</v>
       </c>
-      <c r="N13" s="58">
+      <c r="N13" s="71">
         <v>7.34</v>
       </c>
-      <c r="O13" s="58" t="s">
+      <c r="O13" s="71" t="s">
         <v>17</v>
       </c>
-      <c r="P13" s="58">
+      <c r="P13" s="71">
         <v>4.5999999999999996</v>
       </c>
-      <c r="Q13" s="58">
+      <c r="Q13" s="71">
         <v>7.23</v>
       </c>
-      <c r="R13" s="58" t="s">
+      <c r="R13" s="71" t="s">
         <v>256</v>
       </c>
-      <c r="S13" s="58" t="s">
+      <c r="S13" s="71" t="s">
         <v>17</v>
       </c>
-      <c r="T13" s="58" t="s">
+      <c r="T13" s="71" t="s">
         <v>17</v>
       </c>
-      <c r="U13" s="58" t="s">
+      <c r="U13" s="71" t="s">
         <v>17</v>
       </c>
-      <c r="V13" s="58">
+      <c r="V13" s="71">
         <v>1.6</v>
       </c>
-      <c r="W13" s="58" t="s">
+      <c r="W13" s="71" t="s">
         <v>17</v>
       </c>
-      <c r="X13" s="58" t="s">
+      <c r="X13" s="71" t="s">
         <v>17</v>
       </c>
-      <c r="Y13" s="58"/>
-      <c r="Z13" s="58"/>
+      <c r="Y13" s="71"/>
+      <c r="Z13" s="71"/>
       <c r="AA13" s="58"/>
       <c r="AB13" s="58"/>
       <c r="AC13" s="58"/>
@@ -7238,31 +7266,31 @@
     </row>
     <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A14" s="58"/>
-      <c r="B14" s="58"/>
-      <c r="C14" s="58"/>
-      <c r="D14" s="58"/>
-      <c r="E14" s="58"/>
-      <c r="F14" s="58"/>
-      <c r="G14" s="58"/>
-      <c r="H14" s="58"/>
-      <c r="I14" s="58"/>
-      <c r="J14" s="58"/>
-      <c r="K14" s="58"/>
-      <c r="L14" s="58"/>
-      <c r="M14" s="58"/>
-      <c r="N14" s="58"/>
-      <c r="O14" s="58"/>
-      <c r="P14" s="58"/>
-      <c r="Q14" s="58"/>
-      <c r="R14" s="58"/>
-      <c r="S14" s="58"/>
-      <c r="T14" s="58"/>
-      <c r="U14" s="58"/>
-      <c r="V14" s="58"/>
-      <c r="W14" s="58"/>
-      <c r="X14" s="58"/>
-      <c r="Y14" s="58"/>
-      <c r="Z14" s="58"/>
+      <c r="B14" s="73"/>
+      <c r="C14" s="73"/>
+      <c r="D14" s="73"/>
+      <c r="E14" s="73"/>
+      <c r="F14" s="73"/>
+      <c r="G14" s="73"/>
+      <c r="H14" s="73"/>
+      <c r="I14" s="73"/>
+      <c r="J14" s="73"/>
+      <c r="K14" s="73"/>
+      <c r="L14" s="73"/>
+      <c r="M14" s="73"/>
+      <c r="N14" s="73"/>
+      <c r="O14" s="73"/>
+      <c r="P14" s="73"/>
+      <c r="Q14" s="73"/>
+      <c r="R14" s="73"/>
+      <c r="S14" s="73"/>
+      <c r="T14" s="73"/>
+      <c r="U14" s="73"/>
+      <c r="V14" s="73"/>
+      <c r="W14" s="73"/>
+      <c r="X14" s="73"/>
+      <c r="Y14" s="73"/>
+      <c r="Z14" s="73"/>
       <c r="AA14" s="58"/>
       <c r="AB14" s="58"/>
       <c r="AC14" s="58"/>
@@ -7276,34 +7304,68 @@
       <c r="AK14" s="58"/>
     </row>
     <row r="15" spans="1:37" x14ac:dyDescent="0.2">
-      <c r="A15" s="60" t="s">
+      <c r="A15" s="74" t="s">
         <v>303</v>
       </c>
-      <c r="B15" s="58"/>
-      <c r="C15" s="58"/>
-      <c r="D15" s="58"/>
-      <c r="E15" s="58"/>
-      <c r="F15" s="58"/>
-      <c r="G15" s="58"/>
-      <c r="H15" s="58"/>
-      <c r="I15" s="58"/>
-      <c r="J15" s="58"/>
-      <c r="K15" s="58"/>
-      <c r="L15" s="58"/>
-      <c r="M15" s="58"/>
-      <c r="N15" s="58"/>
-      <c r="O15" s="58"/>
-      <c r="P15" s="58"/>
-      <c r="Q15" s="58"/>
-      <c r="R15" s="58"/>
-      <c r="S15" s="58"/>
-      <c r="T15" s="58"/>
-      <c r="U15" s="58"/>
-      <c r="V15" s="58"/>
-      <c r="W15" s="58"/>
-      <c r="X15" s="58"/>
-      <c r="Y15" s="58"/>
-      <c r="Z15" s="58"/>
+      <c r="B15" s="71" t="s">
+        <v>118</v>
+      </c>
+      <c r="C15" s="71" t="s">
+        <v>119</v>
+      </c>
+      <c r="D15" s="71" t="s">
+        <v>259</v>
+      </c>
+      <c r="E15" s="71" t="s">
+        <v>120</v>
+      </c>
+      <c r="F15" s="71" t="s">
+        <v>121</v>
+      </c>
+      <c r="G15" s="71" t="s">
+        <v>260</v>
+      </c>
+      <c r="H15" s="71" t="s">
+        <v>122</v>
+      </c>
+      <c r="I15" s="71" t="s">
+        <v>261</v>
+      </c>
+      <c r="J15" s="71" t="s">
+        <v>262</v>
+      </c>
+      <c r="K15" s="71" t="s">
+        <v>263</v>
+      </c>
+      <c r="L15" s="71" t="s">
+        <v>123</v>
+      </c>
+      <c r="M15" s="71" t="s">
+        <v>124</v>
+      </c>
+      <c r="N15" s="71" t="s">
+        <v>125</v>
+      </c>
+      <c r="O15" s="71" t="s">
+        <v>126</v>
+      </c>
+      <c r="P15" s="71" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q15" s="71" t="s">
+        <v>128</v>
+      </c>
+      <c r="R15" s="71" t="s">
+        <v>264</v>
+      </c>
+      <c r="S15" s="71"/>
+      <c r="T15" s="71"/>
+      <c r="U15" s="71"/>
+      <c r="V15" s="71"/>
+      <c r="W15" s="71"/>
+      <c r="X15" s="71"/>
+      <c r="Y15" s="71"/>
+      <c r="Z15" s="71"/>
       <c r="AA15" s="58"/>
       <c r="AB15" s="58"/>
       <c r="AC15" s="58"/>
@@ -7881,34 +7943,82 @@
       <c r="AK23" s="58"/>
     </row>
     <row r="24" spans="1:37" x14ac:dyDescent="0.2">
-      <c r="A24" s="60" t="s">
+      <c r="A24" s="74" t="s">
         <v>308</v>
       </c>
-      <c r="B24" s="58"/>
-      <c r="C24" s="58"/>
-      <c r="D24" s="58"/>
-      <c r="E24" s="58"/>
-      <c r="F24" s="58"/>
-      <c r="G24" s="58"/>
-      <c r="H24" s="58"/>
-      <c r="I24" s="58"/>
-      <c r="J24" s="58"/>
-      <c r="K24" s="58"/>
-      <c r="L24" s="58"/>
-      <c r="M24" s="58"/>
-      <c r="N24" s="58"/>
-      <c r="O24" s="58"/>
-      <c r="P24" s="58"/>
-      <c r="Q24" s="58"/>
-      <c r="R24" s="58"/>
-      <c r="S24" s="58"/>
-      <c r="T24" s="58"/>
-      <c r="U24" s="58"/>
-      <c r="V24" s="58"/>
-      <c r="W24" s="58"/>
-      <c r="X24" s="58"/>
-      <c r="Y24" s="58"/>
-      <c r="Z24" s="58"/>
+      <c r="B24" s="71" t="s">
+        <v>118</v>
+      </c>
+      <c r="C24" s="71" t="s">
+        <v>119</v>
+      </c>
+      <c r="D24" s="71" t="s">
+        <v>259</v>
+      </c>
+      <c r="E24" s="71" t="s">
+        <v>120</v>
+      </c>
+      <c r="F24" s="71" t="s">
+        <v>121</v>
+      </c>
+      <c r="G24" s="71" t="s">
+        <v>260</v>
+      </c>
+      <c r="H24" s="71" t="s">
+        <v>122</v>
+      </c>
+      <c r="I24" s="71" t="s">
+        <v>261</v>
+      </c>
+      <c r="J24" s="71" t="s">
+        <v>262</v>
+      </c>
+      <c r="K24" s="71" t="s">
+        <v>263</v>
+      </c>
+      <c r="L24" s="71" t="s">
+        <v>123</v>
+      </c>
+      <c r="M24" s="71" t="s">
+        <v>124</v>
+      </c>
+      <c r="N24" s="71" t="s">
+        <v>125</v>
+      </c>
+      <c r="O24" s="71" t="s">
+        <v>126</v>
+      </c>
+      <c r="P24" s="71" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q24" s="71" t="s">
+        <v>128</v>
+      </c>
+      <c r="R24" s="71" t="s">
+        <v>264</v>
+      </c>
+      <c r="S24" s="71" t="s">
+        <v>265</v>
+      </c>
+      <c r="T24" s="71" t="s">
+        <v>266</v>
+      </c>
+      <c r="U24" s="71" t="s">
+        <v>267</v>
+      </c>
+      <c r="V24" s="71" t="s">
+        <v>268</v>
+      </c>
+      <c r="W24" s="71" t="s">
+        <v>269</v>
+      </c>
+      <c r="X24" s="71" t="s">
+        <v>270</v>
+      </c>
+      <c r="Y24" s="71" t="s">
+        <v>271</v>
+      </c>
+      <c r="Z24" s="71"/>
       <c r="AA24" s="58"/>
       <c r="AB24" s="58"/>
       <c r="AC24" s="58"/>
@@ -8560,34 +8670,82 @@
       <c r="AK32" s="58"/>
     </row>
     <row r="33" spans="1:37" x14ac:dyDescent="0.2">
-      <c r="A33" s="60" t="s">
+      <c r="A33" s="74" t="s">
         <v>305</v>
       </c>
-      <c r="B33" s="58"/>
-      <c r="C33" s="58"/>
-      <c r="D33" s="58"/>
-      <c r="E33" s="58"/>
-      <c r="F33" s="58"/>
-      <c r="G33" s="58"/>
-      <c r="H33" s="58"/>
-      <c r="I33" s="58"/>
-      <c r="J33" s="58"/>
-      <c r="K33" s="58"/>
-      <c r="L33" s="58"/>
-      <c r="M33" s="58"/>
-      <c r="N33" s="58"/>
-      <c r="O33" s="58"/>
-      <c r="P33" s="58"/>
-      <c r="Q33" s="58"/>
-      <c r="R33" s="58"/>
-      <c r="S33" s="58"/>
-      <c r="T33" s="58"/>
-      <c r="U33" s="58"/>
-      <c r="V33" s="58"/>
-      <c r="W33" s="58"/>
-      <c r="X33" s="58"/>
-      <c r="Y33" s="58"/>
-      <c r="Z33" s="58"/>
+      <c r="B33" s="71" t="s">
+        <v>118</v>
+      </c>
+      <c r="C33" s="71" t="s">
+        <v>119</v>
+      </c>
+      <c r="D33" s="71" t="s">
+        <v>259</v>
+      </c>
+      <c r="E33" s="71" t="s">
+        <v>120</v>
+      </c>
+      <c r="F33" s="71" t="s">
+        <v>121</v>
+      </c>
+      <c r="G33" s="71" t="s">
+        <v>260</v>
+      </c>
+      <c r="H33" s="71" t="s">
+        <v>122</v>
+      </c>
+      <c r="I33" s="71" t="s">
+        <v>261</v>
+      </c>
+      <c r="J33" s="71" t="s">
+        <v>262</v>
+      </c>
+      <c r="K33" s="71" t="s">
+        <v>263</v>
+      </c>
+      <c r="L33" s="71" t="s">
+        <v>123</v>
+      </c>
+      <c r="M33" s="71" t="s">
+        <v>124</v>
+      </c>
+      <c r="N33" s="71" t="s">
+        <v>125</v>
+      </c>
+      <c r="O33" s="71" t="s">
+        <v>126</v>
+      </c>
+      <c r="P33" s="71" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q33" s="71" t="s">
+        <v>128</v>
+      </c>
+      <c r="R33" s="71" t="s">
+        <v>264</v>
+      </c>
+      <c r="S33" s="71" t="s">
+        <v>265</v>
+      </c>
+      <c r="T33" s="71" t="s">
+        <v>266</v>
+      </c>
+      <c r="U33" s="71" t="s">
+        <v>267</v>
+      </c>
+      <c r="V33" s="71" t="s">
+        <v>268</v>
+      </c>
+      <c r="W33" s="71" t="s">
+        <v>269</v>
+      </c>
+      <c r="X33" s="71" t="s">
+        <v>270</v>
+      </c>
+      <c r="Y33" s="71" t="s">
+        <v>271</v>
+      </c>
+      <c r="Z33" s="71"/>
       <c r="AA33" s="58"/>
       <c r="AB33" s="58"/>
       <c r="AC33" s="58"/>
@@ -9031,33 +9189,81 @@
       <c r="AK39" s="58"/>
     </row>
     <row r="40" spans="1:37" x14ac:dyDescent="0.2">
-      <c r="A40" s="60" t="s">
+      <c r="A40" s="74" t="s">
         <v>307</v>
       </c>
-      <c r="B40" s="58"/>
-      <c r="C40" s="58"/>
-      <c r="D40" s="58"/>
-      <c r="E40" s="58"/>
-      <c r="F40" s="58"/>
-      <c r="G40" s="58"/>
-      <c r="H40" s="58"/>
-      <c r="I40" s="58"/>
-      <c r="J40" s="58"/>
-      <c r="K40" s="58"/>
-      <c r="L40" s="58"/>
-      <c r="M40" s="58"/>
-      <c r="N40" s="58"/>
-      <c r="O40" s="58"/>
-      <c r="P40" s="58"/>
-      <c r="Q40" s="58"/>
-      <c r="R40" s="58"/>
-      <c r="S40" s="58"/>
-      <c r="T40" s="58"/>
-      <c r="U40" s="58"/>
-      <c r="V40" s="58"/>
-      <c r="W40" s="58"/>
-      <c r="X40" s="58"/>
-      <c r="Y40" s="58"/>
+      <c r="B40" s="71" t="s">
+        <v>118</v>
+      </c>
+      <c r="C40" s="71" t="s">
+        <v>119</v>
+      </c>
+      <c r="D40" s="71" t="s">
+        <v>259</v>
+      </c>
+      <c r="E40" s="71" t="s">
+        <v>120</v>
+      </c>
+      <c r="F40" s="71" t="s">
+        <v>121</v>
+      </c>
+      <c r="G40" s="71" t="s">
+        <v>260</v>
+      </c>
+      <c r="H40" s="71" t="s">
+        <v>122</v>
+      </c>
+      <c r="I40" s="71" t="s">
+        <v>261</v>
+      </c>
+      <c r="J40" s="71" t="s">
+        <v>262</v>
+      </c>
+      <c r="K40" s="71" t="s">
+        <v>263</v>
+      </c>
+      <c r="L40" s="71" t="s">
+        <v>123</v>
+      </c>
+      <c r="M40" s="71" t="s">
+        <v>124</v>
+      </c>
+      <c r="N40" s="71" t="s">
+        <v>125</v>
+      </c>
+      <c r="O40" s="71" t="s">
+        <v>126</v>
+      </c>
+      <c r="P40" s="71" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q40" s="71" t="s">
+        <v>128</v>
+      </c>
+      <c r="R40" s="71" t="s">
+        <v>346</v>
+      </c>
+      <c r="S40" s="71" t="s">
+        <v>265</v>
+      </c>
+      <c r="T40" s="71" t="s">
+        <v>266</v>
+      </c>
+      <c r="U40" s="71" t="s">
+        <v>267</v>
+      </c>
+      <c r="V40" s="71" t="s">
+        <v>268</v>
+      </c>
+      <c r="W40" s="71" t="s">
+        <v>269</v>
+      </c>
+      <c r="X40" s="71" t="s">
+        <v>270</v>
+      </c>
+      <c r="Y40" s="71" t="s">
+        <v>271</v>
+      </c>
       <c r="Z40" s="58"/>
       <c r="AA40" s="58"/>
       <c r="AB40" s="58"/>
@@ -9751,26 +9957,28 @@
       <c r="AK49" s="58"/>
     </row>
     <row r="50" spans="1:37" x14ac:dyDescent="0.2">
-      <c r="A50" s="58" t="s">
+      <c r="A50" s="71" t="s">
         <v>313</v>
       </c>
-      <c r="B50" s="58" t="s">
+      <c r="B50" s="71" t="s">
         <v>314</v>
       </c>
-      <c r="C50" s="58" t="s">
+      <c r="C50" s="71" t="s">
         <v>315</v>
       </c>
-      <c r="D50" s="58" t="s">
+      <c r="D50" s="71" t="s">
         <v>316</v>
       </c>
-      <c r="E50" s="58" t="s">
+      <c r="E50" s="71" t="s">
         <v>317</v>
       </c>
-      <c r="F50" s="58" t="s">
+      <c r="F50" s="71" t="s">
         <v>318</v>
       </c>
-      <c r="G50" s="58"/>
-      <c r="H50" s="58"/>
+      <c r="G50" s="71"/>
+      <c r="H50" s="71" t="s">
+        <v>347</v>
+      </c>
       <c r="I50" s="58"/>
       <c r="J50" s="58"/>
       <c r="K50" s="58"/>
@@ -9984,7 +10192,7 @@
       </c>
       <c r="G54" s="58"/>
       <c r="H54" s="58">
-        <f>AVERAGE(D54,E54,D59,E59)</f>
+        <f>AVERAGE(D54,E54,D58,E58)</f>
         <v>0.35</v>
       </c>
       <c r="I54" s="58"/>
@@ -10092,7 +10300,7 @@
       </c>
       <c r="G56" s="58"/>
       <c r="H56" s="58">
-        <f>AVERAGE(E56,D56,D60,E60)</f>
+        <f>AVERAGE(E56,D56,D59,E59)</f>
         <v>1.1312500000000001</v>
       </c>
       <c r="I56" s="58"/>
@@ -10180,13 +10388,27 @@
       <c r="AK57" s="58"/>
     </row>
     <row r="58" spans="1:37" x14ac:dyDescent="0.2">
-      <c r="A58" s="58"/>
-      <c r="B58" s="58"/>
-      <c r="C58" s="58"/>
-      <c r="D58" s="58"/>
-      <c r="E58" s="58"/>
-      <c r="F58" s="58"/>
-      <c r="G58" s="58"/>
+      <c r="A58" s="58" t="s">
+        <v>320</v>
+      </c>
+      <c r="B58" s="58">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="C58" s="58">
+        <v>19.5</v>
+      </c>
+      <c r="D58" s="58">
+        <v>0.36</v>
+      </c>
+      <c r="E58" s="58">
+        <v>0.36</v>
+      </c>
+      <c r="F58" s="58">
+        <v>540</v>
+      </c>
+      <c r="G58" s="58" t="s">
+        <v>321</v>
+      </c>
       <c r="H58" s="58"/>
       <c r="I58" s="58"/>
       <c r="J58" s="58"/>
@@ -10220,25 +10442,25 @@
     </row>
     <row r="59" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A59" s="58" t="s">
-        <v>320</v>
-      </c>
-      <c r="B59" s="58">
-        <v>19.600000000000001</v>
-      </c>
-      <c r="C59" s="58">
-        <v>19.5</v>
+        <v>322</v>
+      </c>
+      <c r="B59" s="58" t="s">
+        <v>17</v>
+      </c>
+      <c r="C59" s="58" t="s">
+        <v>17</v>
       </c>
       <c r="D59" s="58">
-        <v>0.36</v>
+        <v>2.04</v>
       </c>
       <c r="E59" s="58">
-        <v>0.36</v>
+        <v>1.6850000000000001</v>
       </c>
       <c r="F59" s="58">
-        <v>540</v>
+        <v>275</v>
       </c>
       <c r="G59" s="58" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="H59" s="58"/>
       <c r="I59" s="58"/>
@@ -10272,27 +10494,13 @@
       <c r="AK59" s="58"/>
     </row>
     <row r="60" spans="1:37" x14ac:dyDescent="0.2">
-      <c r="A60" s="58" t="s">
-        <v>322</v>
-      </c>
-      <c r="B60" s="58" t="s">
-        <v>17</v>
-      </c>
-      <c r="C60" s="58" t="s">
-        <v>17</v>
-      </c>
-      <c r="D60" s="58">
-        <v>2.04</v>
-      </c>
-      <c r="E60" s="58">
-        <v>1.6850000000000001</v>
-      </c>
-      <c r="F60" s="58">
-        <v>275</v>
-      </c>
-      <c r="G60" s="58" t="s">
-        <v>323</v>
-      </c>
+      <c r="A60" s="58"/>
+      <c r="B60" s="58"/>
+      <c r="C60" s="58"/>
+      <c r="D60" s="58"/>
+      <c r="E60" s="58"/>
+      <c r="F60" s="58"/>
+      <c r="G60" s="58"/>
       <c r="H60" s="58"/>
       <c r="I60" s="58"/>
       <c r="J60" s="58"/>
@@ -10325,7 +10533,9 @@
       <c r="AK60" s="58"/>
     </row>
     <row r="61" spans="1:37" x14ac:dyDescent="0.2">
-      <c r="A61" s="58"/>
+      <c r="A61" s="64" t="s">
+        <v>325</v>
+      </c>
       <c r="B61" s="58"/>
       <c r="C61" s="58"/>
       <c r="D61" s="58"/>
@@ -10364,33 +10574,81 @@
       <c r="AK61" s="58"/>
     </row>
     <row r="62" spans="1:37" x14ac:dyDescent="0.2">
-      <c r="A62" s="64" t="s">
-        <v>325</v>
-      </c>
-      <c r="B62" s="58"/>
-      <c r="C62" s="58"/>
-      <c r="D62" s="58"/>
-      <c r="E62" s="58"/>
-      <c r="F62" s="58"/>
-      <c r="G62" s="58"/>
-      <c r="H62" s="58"/>
-      <c r="I62" s="58"/>
-      <c r="J62" s="58"/>
-      <c r="K62" s="58"/>
-      <c r="L62" s="58"/>
-      <c r="M62" s="58"/>
-      <c r="N62" s="58"/>
-      <c r="O62" s="58"/>
-      <c r="P62" s="58"/>
-      <c r="Q62" s="58"/>
-      <c r="R62" s="58"/>
-      <c r="S62" s="58"/>
-      <c r="T62" s="58"/>
-      <c r="U62" s="58"/>
-      <c r="V62" s="58"/>
-      <c r="W62" s="58"/>
-      <c r="X62" s="58"/>
-      <c r="Y62" s="58"/>
+      <c r="A62" s="65" t="s">
+        <v>117</v>
+      </c>
+      <c r="B62" s="65" t="s">
+        <v>118</v>
+      </c>
+      <c r="C62" s="65" t="s">
+        <v>119</v>
+      </c>
+      <c r="D62" s="65" t="s">
+        <v>259</v>
+      </c>
+      <c r="E62" s="65" t="s">
+        <v>120</v>
+      </c>
+      <c r="F62" s="65" t="s">
+        <v>121</v>
+      </c>
+      <c r="G62" s="65" t="s">
+        <v>260</v>
+      </c>
+      <c r="H62" s="65" t="s">
+        <v>122</v>
+      </c>
+      <c r="I62" s="65" t="s">
+        <v>261</v>
+      </c>
+      <c r="J62" s="65" t="s">
+        <v>262</v>
+      </c>
+      <c r="K62" s="65" t="s">
+        <v>263</v>
+      </c>
+      <c r="L62" s="65" t="s">
+        <v>123</v>
+      </c>
+      <c r="M62" s="65" t="s">
+        <v>124</v>
+      </c>
+      <c r="N62" s="65" t="s">
+        <v>125</v>
+      </c>
+      <c r="O62" s="65" t="s">
+        <v>126</v>
+      </c>
+      <c r="P62" s="65" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q62" s="65" t="s">
+        <v>128</v>
+      </c>
+      <c r="R62" s="65" t="s">
+        <v>264</v>
+      </c>
+      <c r="S62" s="65" t="s">
+        <v>265</v>
+      </c>
+      <c r="T62" s="65" t="s">
+        <v>266</v>
+      </c>
+      <c r="U62" s="65" t="s">
+        <v>267</v>
+      </c>
+      <c r="V62" s="65" t="s">
+        <v>268</v>
+      </c>
+      <c r="W62" s="65" t="s">
+        <v>269</v>
+      </c>
+      <c r="X62" s="65" t="s">
+        <v>270</v>
+      </c>
+      <c r="Y62" s="65" t="s">
+        <v>324</v>
+      </c>
       <c r="Z62" s="58"/>
       <c r="AA62" s="58"/>
       <c r="AB62" s="58"/>
@@ -10405,80 +10663,72 @@
       <c r="AK62" s="58"/>
     </row>
     <row r="63" spans="1:37" x14ac:dyDescent="0.2">
-      <c r="A63" s="65" t="s">
-        <v>117</v>
-      </c>
-      <c r="B63" s="65" t="s">
-        <v>118</v>
-      </c>
-      <c r="C63" s="65" t="s">
-        <v>119</v>
-      </c>
-      <c r="D63" s="65" t="s">
-        <v>259</v>
-      </c>
-      <c r="E63" s="65" t="s">
-        <v>120</v>
-      </c>
-      <c r="F63" s="65" t="s">
-        <v>121</v>
-      </c>
-      <c r="G63" s="65" t="s">
-        <v>260</v>
-      </c>
-      <c r="H63" s="65" t="s">
-        <v>122</v>
-      </c>
-      <c r="I63" s="65" t="s">
-        <v>261</v>
-      </c>
-      <c r="J63" s="65" t="s">
-        <v>262</v>
-      </c>
-      <c r="K63" s="65" t="s">
-        <v>263</v>
-      </c>
-      <c r="L63" s="65" t="s">
-        <v>123</v>
-      </c>
-      <c r="M63" s="65" t="s">
-        <v>124</v>
-      </c>
-      <c r="N63" s="65" t="s">
-        <v>125</v>
-      </c>
-      <c r="O63" s="65" t="s">
-        <v>126</v>
-      </c>
-      <c r="P63" s="65" t="s">
-        <v>127</v>
-      </c>
-      <c r="Q63" s="65" t="s">
-        <v>128</v>
-      </c>
-      <c r="R63" s="65" t="s">
-        <v>264</v>
-      </c>
-      <c r="S63" s="65" t="s">
-        <v>265</v>
-      </c>
-      <c r="T63" s="65" t="s">
-        <v>266</v>
-      </c>
-      <c r="U63" s="65" t="s">
-        <v>267</v>
-      </c>
-      <c r="V63" s="65" t="s">
-        <v>268</v>
-      </c>
-      <c r="W63" s="65" t="s">
-        <v>269</v>
-      </c>
-      <c r="X63" s="65" t="s">
-        <v>270</v>
-      </c>
-      <c r="Y63" s="65" t="s">
-        <v>324</v>
+      <c r="A63" s="58" t="s">
+        <v>129</v>
+      </c>
+      <c r="B63" s="59">
+        <v>44772</v>
+      </c>
+      <c r="C63" s="58" t="s">
+        <v>130</v>
+      </c>
+      <c r="D63" s="58" t="s">
+        <v>253</v>
+      </c>
+      <c r="E63" s="58">
+        <v>37.85989</v>
+      </c>
+      <c r="F63" s="58">
+        <v>-119.61614</v>
+      </c>
+      <c r="G63" s="58">
+        <v>2513</v>
+      </c>
+      <c r="H63" s="58">
+        <v>17.8</v>
+      </c>
+      <c r="I63" s="58">
+        <v>17</v>
+      </c>
+      <c r="J63" s="58">
+        <v>12</v>
+      </c>
+      <c r="K63" s="58">
+        <v>480</v>
+      </c>
+      <c r="L63" s="58">
+        <v>21.4</v>
+      </c>
+      <c r="M63" s="58">
+        <v>78.2</v>
+      </c>
+      <c r="N63" s="58">
+        <v>6.87</v>
+      </c>
+      <c r="O63" s="58">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="P63" s="58">
+        <v>15</v>
+      </c>
+      <c r="Q63" s="58">
+        <v>8.36</v>
+      </c>
+      <c r="R63" s="58"/>
+      <c r="S63" s="58"/>
+      <c r="T63" s="58"/>
+      <c r="U63" s="58"/>
+      <c r="V63" s="58">
+        <v>3.1</v>
+      </c>
+      <c r="W63" s="58">
+        <v>217.44</v>
+      </c>
+      <c r="X63" s="58">
+        <v>32.97</v>
+      </c>
+      <c r="Y63" s="58">
+        <v>0.71</v>
       </c>
       <c r="Z63" s="58"/>
       <c r="AA63" s="58"/>
@@ -10501,65 +10751,65 @@
         <v>44772</v>
       </c>
       <c r="C64" s="58" t="s">
-        <v>130</v>
+        <v>18</v>
       </c>
       <c r="D64" s="58" t="s">
         <v>253</v>
       </c>
       <c r="E64" s="58">
-        <v>37.85989</v>
+        <v>37.834271000000001</v>
       </c>
       <c r="F64" s="58">
-        <v>-119.61614</v>
+        <v>-119.48997</v>
       </c>
       <c r="G64" s="58">
-        <v>2513</v>
+        <v>2714</v>
       </c>
       <c r="H64" s="58">
-        <v>17.8</v>
-      </c>
-      <c r="I64" s="58">
+        <v>2</v>
+      </c>
+      <c r="I64" s="58" t="s">
         <v>17</v>
       </c>
       <c r="J64" s="58">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="K64" s="58">
-        <v>480</v>
+        <v>300</v>
       </c>
       <c r="L64" s="58">
-        <v>21.4</v>
+        <v>21.7</v>
       </c>
       <c r="M64" s="58">
-        <v>78.2</v>
+        <v>60.5</v>
       </c>
       <c r="N64" s="58">
-        <v>6.87</v>
+        <v>5.33</v>
       </c>
       <c r="O64" s="58">
-        <v>16.100000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="P64" s="58">
-        <v>15</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="Q64" s="58">
-        <v>8.36</v>
+        <v>7.8</v>
       </c>
       <c r="R64" s="58"/>
       <c r="S64" s="58"/>
       <c r="T64" s="58"/>
       <c r="U64" s="58"/>
       <c r="V64" s="58">
-        <v>3.1</v>
+        <v>0.8</v>
       </c>
       <c r="W64" s="58">
-        <v>217.44</v>
+        <v>137.16</v>
       </c>
       <c r="X64" s="58">
-        <v>32.97</v>
+        <v>22.6</v>
       </c>
       <c r="Y64" s="58">
-        <v>0.71</v>
+        <v>1.58</v>
       </c>
       <c r="Z64" s="58"/>
       <c r="AA64" s="58"/>
@@ -10579,68 +10829,68 @@
         <v>129</v>
       </c>
       <c r="B65" s="59">
-        <v>44772</v>
+        <v>44779</v>
       </c>
       <c r="C65" s="58" t="s">
-        <v>18</v>
+        <v>254</v>
       </c>
       <c r="D65" s="58" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="E65" s="58">
-        <v>37.834271000000001</v>
+        <v>37.808819999999997</v>
       </c>
       <c r="F65" s="58">
-        <v>-119.48997</v>
+        <v>-119.44947999999999</v>
       </c>
       <c r="G65" s="58">
-        <v>2714</v>
+        <v>2830</v>
       </c>
       <c r="H65" s="58">
-        <v>2</v>
-      </c>
-      <c r="I65" s="58" t="s">
+        <v>16.8</v>
+      </c>
+      <c r="I65" s="58">
+        <v>13</v>
+      </c>
+      <c r="J65" s="58">
+        <v>12</v>
+      </c>
+      <c r="K65" s="58">
+        <v>180</v>
+      </c>
+      <c r="L65" s="58">
+        <v>18.79</v>
+      </c>
+      <c r="M65" s="58">
+        <v>72.97</v>
+      </c>
+      <c r="N65" s="58">
+        <v>6.8</v>
+      </c>
+      <c r="O65" s="58" t="s">
         <v>17</v>
       </c>
-      <c r="J65" s="58">
-        <v>1</v>
-      </c>
-      <c r="K65" s="58">
-        <v>300</v>
-      </c>
-      <c r="L65" s="58">
-        <v>21.7</v>
-      </c>
-      <c r="M65" s="58">
-        <v>60.5</v>
-      </c>
-      <c r="N65" s="58">
-        <v>5.33</v>
-      </c>
-      <c r="O65" s="58">
-        <v>10.5</v>
-      </c>
       <c r="P65" s="58">
-        <v>9.8000000000000007</v>
+        <v>0.1</v>
       </c>
       <c r="Q65" s="58">
-        <v>7.8</v>
+        <v>6.92</v>
       </c>
       <c r="R65" s="58"/>
       <c r="S65" s="58"/>
       <c r="T65" s="58"/>
       <c r="U65" s="58"/>
       <c r="V65" s="58">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="W65" s="58">
-        <v>137.16</v>
+        <v>157.75</v>
       </c>
       <c r="X65" s="58">
-        <v>22.6</v>
+        <v>16.25</v>
       </c>
       <c r="Y65" s="58">
-        <v>1.58</v>
+        <v>1.92</v>
       </c>
       <c r="Z65" s="58"/>
       <c r="AA65" s="58"/>
@@ -10660,68 +10910,68 @@
         <v>129</v>
       </c>
       <c r="B66" s="59">
-        <v>44779</v>
+        <v>44741</v>
       </c>
       <c r="C66" s="58" t="s">
-        <v>254</v>
+        <v>131</v>
       </c>
       <c r="D66" s="58" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="E66" s="58">
-        <v>37.808819999999997</v>
+        <v>38.050952000000002</v>
       </c>
       <c r="F66" s="58">
-        <v>-119.44947999999999</v>
+        <v>-119.27033</v>
       </c>
       <c r="G66" s="58">
-        <v>2830</v>
+        <v>3054</v>
       </c>
       <c r="H66" s="58">
-        <v>16.8</v>
+        <v>52</v>
       </c>
       <c r="I66" s="58">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J66" s="58">
-        <v>12</v>
+        <v>49.2</v>
       </c>
       <c r="K66" s="58">
-        <v>180</v>
+        <v>600</v>
       </c>
       <c r="L66" s="58">
-        <v>18.79</v>
+        <v>12.8</v>
       </c>
       <c r="M66" s="58">
-        <v>72.97</v>
+        <v>73.8</v>
       </c>
       <c r="N66" s="58">
-        <v>6.8</v>
-      </c>
-      <c r="O66" s="58" t="s">
-        <v>17</v>
+        <v>7.92</v>
+      </c>
+      <c r="O66" s="58">
+        <v>97.5</v>
       </c>
       <c r="P66" s="58">
-        <v>0.1</v>
+        <v>74.7</v>
       </c>
       <c r="Q66" s="58">
-        <v>6.92</v>
+        <v>7.97</v>
       </c>
       <c r="R66" s="58"/>
       <c r="S66" s="58"/>
       <c r="T66" s="58"/>
       <c r="U66" s="58"/>
       <c r="V66" s="58">
-        <v>1.9</v>
+        <v>7.6</v>
       </c>
       <c r="W66" s="58">
-        <v>157.75</v>
+        <v>947.92</v>
       </c>
       <c r="X66" s="58">
-        <v>16.25</v>
+        <v>199.69</v>
       </c>
       <c r="Y66" s="58">
-        <v>1.92</v>
+        <v>0.35</v>
       </c>
       <c r="Z66" s="58"/>
       <c r="AA66" s="58"/>
@@ -10741,68 +10991,68 @@
         <v>129</v>
       </c>
       <c r="B67" s="59">
-        <v>44741</v>
+        <v>44784</v>
       </c>
       <c r="C67" s="58" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D67" s="58" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="E67" s="58">
-        <v>38.050952000000002</v>
+        <v>37.98977</v>
       </c>
       <c r="F67" s="58">
-        <v>-119.27033</v>
+        <v>-119.30625999999999</v>
       </c>
       <c r="G67" s="58">
-        <v>3054</v>
+        <v>3140</v>
       </c>
       <c r="H67" s="58">
-        <v>52</v>
-      </c>
-      <c r="I67" s="58">
-        <v>16</v>
-      </c>
-      <c r="J67" s="58">
-        <v>49.2</v>
-      </c>
-      <c r="K67" s="58">
-        <v>600</v>
+        <v>34.6</v>
+      </c>
+      <c r="I67" s="58" t="s">
+        <v>17</v>
+      </c>
+      <c r="J67" s="58" t="s">
+        <v>17</v>
+      </c>
+      <c r="K67" s="58" t="s">
+        <v>17</v>
       </c>
       <c r="L67" s="58">
-        <v>12.8</v>
+        <v>13.85</v>
       </c>
       <c r="M67" s="58">
-        <v>73.8</v>
+        <v>71</v>
       </c>
       <c r="N67" s="58">
-        <v>7.92</v>
-      </c>
-      <c r="O67" s="58">
-        <v>97.5</v>
+        <v>7.34</v>
+      </c>
+      <c r="O67" s="58" t="s">
+        <v>17</v>
       </c>
       <c r="P67" s="58">
-        <v>74.7</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="Q67" s="58">
-        <v>7.97</v>
+        <v>7.23</v>
       </c>
       <c r="R67" s="58"/>
       <c r="S67" s="58"/>
       <c r="T67" s="58"/>
       <c r="U67" s="58"/>
       <c r="V67" s="58">
-        <v>7.6</v>
+        <v>2.35</v>
       </c>
       <c r="W67" s="58">
-        <v>947.92</v>
+        <v>199.5</v>
       </c>
       <c r="X67" s="58">
-        <v>199.69</v>
+        <v>27.86</v>
       </c>
       <c r="Y67" s="58">
-        <v>0.35</v>
+        <v>0.53</v>
       </c>
       <c r="Z67" s="58"/>
       <c r="AA67" s="58"/>
@@ -10822,68 +11072,68 @@
         <v>129</v>
       </c>
       <c r="B68" s="59">
-        <v>44784</v>
+        <v>44738</v>
       </c>
       <c r="C68" s="58" t="s">
-        <v>133</v>
+        <v>88</v>
       </c>
       <c r="D68" s="58" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="E68" s="58">
-        <v>37.98977</v>
+        <v>37.431525999999998</v>
       </c>
       <c r="F68" s="58">
-        <v>-119.30625999999999</v>
+        <v>-118.74262</v>
       </c>
       <c r="G68" s="58">
-        <v>3140</v>
+        <v>3155</v>
       </c>
       <c r="H68" s="58">
-        <v>34.6</v>
-      </c>
-      <c r="I68" s="58" t="s">
-        <v>17</v>
-      </c>
-      <c r="J68" s="58" t="s">
-        <v>17</v>
-      </c>
-      <c r="K68" s="58" t="s">
-        <v>17</v>
+        <v>18.600000000000001</v>
+      </c>
+      <c r="I68" s="58">
+        <v>19</v>
+      </c>
+      <c r="J68" s="58">
+        <v>16.399999999999999</v>
+      </c>
+      <c r="K68" s="58">
+        <v>300</v>
       </c>
       <c r="L68" s="58">
-        <v>13.85</v>
+        <v>13.1</v>
       </c>
       <c r="M68" s="58">
-        <v>71</v>
+        <v>67.3</v>
       </c>
       <c r="N68" s="58">
-        <v>7.34</v>
-      </c>
-      <c r="O68" s="58" t="s">
-        <v>17</v>
+        <v>7.05</v>
+      </c>
+      <c r="O68" s="58">
+        <v>20</v>
       </c>
       <c r="P68" s="58">
-        <v>4.5999999999999996</v>
+        <v>15.5</v>
       </c>
       <c r="Q68" s="58">
-        <v>7.23</v>
+        <v>6.9</v>
       </c>
       <c r="R68" s="58"/>
       <c r="S68" s="58"/>
       <c r="T68" s="58"/>
       <c r="U68" s="58"/>
       <c r="V68" s="58">
-        <v>2.35</v>
+        <v>0.5</v>
       </c>
       <c r="W68" s="58">
-        <v>199.5</v>
+        <v>240.83</v>
       </c>
       <c r="X68" s="58">
-        <v>27.86</v>
+        <v>136.84</v>
       </c>
       <c r="Y68" s="58">
-        <v>0.53</v>
+        <v>1.1312500000000001</v>
       </c>
       <c r="Z68" s="58"/>
       <c r="AA68" s="58"/>
@@ -10903,68 +11153,68 @@
         <v>129</v>
       </c>
       <c r="B69" s="59">
-        <v>44738</v>
+        <v>44781</v>
       </c>
       <c r="C69" s="58" t="s">
-        <v>88</v>
+        <v>257</v>
       </c>
       <c r="D69" s="58" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="E69" s="58">
-        <v>37.431525999999998</v>
+        <v>37.926450000000003</v>
       </c>
       <c r="F69" s="58">
-        <v>-118.74262</v>
+        <v>-119.27843</v>
       </c>
       <c r="G69" s="58">
-        <v>3155</v>
+        <v>3178</v>
       </c>
       <c r="H69" s="58">
-        <v>18.600000000000001</v>
+        <v>42.5</v>
       </c>
       <c r="I69" s="58">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="J69" s="58">
-        <v>16.399999999999999</v>
+        <v>33</v>
       </c>
       <c r="K69" s="58">
         <v>300</v>
       </c>
       <c r="L69" s="58">
-        <v>13.1</v>
+        <v>15.74</v>
       </c>
       <c r="M69" s="58">
-        <v>67.3</v>
+        <v>43.07</v>
       </c>
       <c r="N69" s="58">
-        <v>7.05</v>
-      </c>
-      <c r="O69" s="58">
-        <v>20</v>
+        <v>7.25</v>
+      </c>
+      <c r="O69" s="58" t="s">
+        <v>17</v>
       </c>
       <c r="P69" s="58">
-        <v>15.5</v>
+        <v>9.2899999999999991</v>
       </c>
       <c r="Q69" s="58">
-        <v>6.9</v>
+        <v>8.9700000000000006</v>
       </c>
       <c r="R69" s="58"/>
       <c r="S69" s="58"/>
       <c r="T69" s="58"/>
       <c r="U69" s="58"/>
       <c r="V69" s="58">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="W69" s="58">
-        <v>240.83</v>
+        <v>277.54000000000002</v>
       </c>
       <c r="X69" s="58">
-        <v>136.84</v>
+        <v>9.91</v>
       </c>
       <c r="Y69" s="58">
-        <v>1.1312500000000001</v>
+        <v>1.01</v>
       </c>
       <c r="Z69" s="58"/>
       <c r="AA69" s="58"/>
@@ -10980,85 +11230,31 @@
       <c r="AK69" s="58"/>
     </row>
     <row r="70" spans="1:37" x14ac:dyDescent="0.2">
-      <c r="A70" s="58" t="s">
-        <v>129</v>
-      </c>
-      <c r="B70" s="59">
-        <v>44781</v>
-      </c>
-      <c r="C70" s="58" t="s">
-        <v>257</v>
-      </c>
-      <c r="D70" s="58" t="s">
-        <v>255</v>
-      </c>
-      <c r="E70" s="58">
-        <v>37.926450000000003</v>
-      </c>
-      <c r="F70" s="58">
-        <v>-119.27843</v>
-      </c>
-      <c r="G70" s="58">
-        <v>3178</v>
-      </c>
-      <c r="H70" s="58">
-        <v>42.5</v>
-      </c>
-      <c r="I70" s="58">
-        <v>36</v>
-      </c>
-      <c r="J70" s="58">
-        <v>33</v>
-      </c>
-      <c r="K70" s="58">
-        <v>300</v>
-      </c>
-      <c r="L70" s="58">
-        <v>15.74</v>
-      </c>
-      <c r="M70" s="58">
-        <v>43.07</v>
-      </c>
-      <c r="N70" s="58">
-        <v>7.25</v>
-      </c>
-      <c r="O70" s="58" t="s">
-        <v>17</v>
-      </c>
-      <c r="P70" s="58">
-        <v>9.2899999999999991</v>
-      </c>
-      <c r="Q70" s="58">
-        <v>8.9700000000000006</v>
-      </c>
+      <c r="A70" s="58"/>
+      <c r="B70" s="58"/>
+      <c r="C70" s="58"/>
+      <c r="D70" s="58"/>
+      <c r="E70" s="58"/>
+      <c r="F70" s="58"/>
+      <c r="G70" s="58"/>
+      <c r="H70" s="58"/>
+      <c r="I70" s="58"/>
+      <c r="J70" s="58"/>
+      <c r="K70" s="58"/>
+      <c r="L70" s="58"/>
+      <c r="M70" s="58"/>
+      <c r="N70" s="58"/>
+      <c r="O70" s="58"/>
+      <c r="P70" s="58"/>
+      <c r="Q70" s="58"/>
       <c r="R70" s="58"/>
       <c r="S70" s="58"/>
       <c r="T70" s="58"/>
       <c r="U70" s="58"/>
-      <c r="V70" s="58">
-        <v>0.7</v>
-      </c>
-      <c r="W70" s="58">
-        <v>277.54000000000002</v>
-      </c>
-      <c r="X70" s="58">
-        <v>9.91</v>
-      </c>
-      <c r="Y70" s="58">
-        <v>1.01</v>
-      </c>
-      <c r="Z70" s="58"/>
-      <c r="AA70" s="58"/>
-      <c r="AB70" s="58"/>
-      <c r="AC70" s="58"/>
-      <c r="AD70" s="58"/>
-      <c r="AE70" s="58"/>
-      <c r="AF70" s="58"/>
-      <c r="AG70" s="58"/>
-      <c r="AH70" s="58"/>
-      <c r="AI70" s="58"/>
-      <c r="AJ70" s="58"/>
-      <c r="AK70" s="58"/>
+      <c r="V70" s="58"/>
+      <c r="W70" s="58"/>
+      <c r="X70" s="58"/>
+      <c r="Y70" s="58"/>
     </row>
     <row r="71" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A71" s="58"/>
@@ -35792,33 +35988,6 @@
       <c r="X986" s="58"/>
       <c r="Y986" s="58"/>
     </row>
-    <row r="987" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A987" s="58"/>
-      <c r="B987" s="58"/>
-      <c r="C987" s="58"/>
-      <c r="D987" s="58"/>
-      <c r="E987" s="58"/>
-      <c r="F987" s="58"/>
-      <c r="G987" s="58"/>
-      <c r="H987" s="58"/>
-      <c r="I987" s="58"/>
-      <c r="J987" s="58"/>
-      <c r="K987" s="58"/>
-      <c r="L987" s="58"/>
-      <c r="M987" s="58"/>
-      <c r="N987" s="58"/>
-      <c r="O987" s="58"/>
-      <c r="P987" s="58"/>
-      <c r="Q987" s="58"/>
-      <c r="R987" s="58"/>
-      <c r="S987" s="58"/>
-      <c r="T987" s="58"/>
-      <c r="U987" s="58"/>
-      <c r="V987" s="58"/>
-      <c r="W987" s="58"/>
-      <c r="X987" s="58"/>
-      <c r="Y987" s="58"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
